--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/181.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/181.xlsx
@@ -426,13 +426,13 @@
         <v>4.837293954832162</v>
       </c>
       <c r="E2">
-        <v>-14.94023031096345</v>
+        <v>-13.92486492591162</v>
       </c>
       <c r="F2">
-        <v>-2.664923523078338</v>
+        <v>-2.133622753168583</v>
       </c>
       <c r="G2">
-        <v>-11.27903311351081</v>
+        <v>-10.87965552074421</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.574745232271779</v>
       </c>
       <c r="E3">
-        <v>-13.86447772501934</v>
+        <v>-13.87976585326923</v>
       </c>
       <c r="F3">
-        <v>-2.764161109566317</v>
+        <v>-2.068138653242477</v>
       </c>
       <c r="G3">
-        <v>-10.18419597712735</v>
+        <v>-11.52788682169782</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.279109221804799</v>
       </c>
       <c r="E4">
-        <v>-15.42072857402133</v>
+        <v>-14.62934151338887</v>
       </c>
       <c r="F4">
-        <v>-2.590933746660287</v>
+        <v>-2.090013351248203</v>
       </c>
       <c r="G4">
-        <v>-10.21919175402299</v>
+        <v>-10.33752720432424</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>3.981620542038723</v>
       </c>
       <c r="E5">
-        <v>-14.17019047680316</v>
+        <v>-14.62981247468567</v>
       </c>
       <c r="F5">
-        <v>-2.719171647552872</v>
+        <v>-1.848941869685491</v>
       </c>
       <c r="G5">
-        <v>-10.31028141453604</v>
+        <v>-10.9113010255541</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>3.694756156419648</v>
       </c>
       <c r="E6">
-        <v>-17.65584748998718</v>
+        <v>-14.94197377345641</v>
       </c>
       <c r="F6">
-        <v>-3.026384952759514</v>
+        <v>-2.227913329527043</v>
       </c>
       <c r="G6">
-        <v>-10.29454308104234</v>
+        <v>-10.39461094105789</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>3.438306770316261</v>
       </c>
       <c r="E7">
-        <v>-15.68681264976402</v>
+        <v>-16.20655014009835</v>
       </c>
       <c r="F7">
-        <v>-2.645065899698429</v>
+        <v>-1.60956025762449</v>
       </c>
       <c r="G7">
-        <v>-9.745475861172059</v>
+        <v>-10.84212386596549</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.228050098697349</v>
       </c>
       <c r="E8">
-        <v>-15.85138645215078</v>
+        <v>-16.20069935168044</v>
       </c>
       <c r="F8">
-        <v>-3.170203616131356</v>
+        <v>-1.580591421181188</v>
       </c>
       <c r="G8">
-        <v>-9.208968851077771</v>
+        <v>-10.13934139561577</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.079019447108236</v>
       </c>
       <c r="E9">
-        <v>-18.65534510211614</v>
+        <v>-17.42818298772556</v>
       </c>
       <c r="F9">
-        <v>-2.23292826578359</v>
+        <v>-1.820880923915658</v>
       </c>
       <c r="G9">
-        <v>-8.064857554887805</v>
+        <v>-9.582471219909424</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.000968479794909</v>
       </c>
       <c r="E10">
-        <v>-17.23067359388102</v>
+        <v>-16.40962955697233</v>
       </c>
       <c r="F10">
-        <v>-2.622135033254133</v>
+        <v>-1.514717160208363</v>
       </c>
       <c r="G10">
-        <v>-8.813931383513157</v>
+        <v>-10.61542432852728</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>2.996930016579974</v>
       </c>
       <c r="E11">
-        <v>-18.39618959160518</v>
+        <v>-18.04314522949319</v>
       </c>
       <c r="F11">
-        <v>-2.45699667803644</v>
+        <v>-1.194083474708967</v>
       </c>
       <c r="G11">
-        <v>-6.58524233156594</v>
+        <v>-10.43207638492582</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.062665087424161</v>
       </c>
       <c r="E12">
-        <v>-18.88737505332115</v>
+        <v>-19.07427423256572</v>
       </c>
       <c r="F12">
-        <v>-3.125446096990696</v>
+        <v>-1.654973843748167</v>
       </c>
       <c r="G12">
-        <v>-8.453694370657363</v>
+        <v>-9.536103719086391</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.186731867959157</v>
       </c>
       <c r="E13">
-        <v>-19.41748274913305</v>
+        <v>-20.19884376831252</v>
       </c>
       <c r="F13">
-        <v>-2.527085672354709</v>
+        <v>-1.4467603835849</v>
       </c>
       <c r="G13">
-        <v>-8.74555206539951</v>
+        <v>-8.93047251813212</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.355811294638842</v>
       </c>
       <c r="E14">
-        <v>-20.80164705736956</v>
+        <v>-19.48089044218845</v>
       </c>
       <c r="F14">
-        <v>-2.14572105908647</v>
+        <v>-1.143706311107715</v>
       </c>
       <c r="G14">
-        <v>-9.082267652198784</v>
+        <v>-8.071710384154096</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.55309886376981</v>
       </c>
       <c r="E15">
-        <v>-20.25401416714798</v>
+        <v>-20.39315153103365</v>
       </c>
       <c r="F15">
-        <v>-1.775626384333318</v>
+        <v>-1.070988078652961</v>
       </c>
       <c r="G15">
-        <v>-9.315045351247097</v>
+        <v>-8.045881507856702</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.760841177793091</v>
       </c>
       <c r="E16">
-        <v>-22.00535620487441</v>
+        <v>-20.83874431644039</v>
       </c>
       <c r="F16">
-        <v>-1.917951501277912</v>
+        <v>-1.092964665849231</v>
       </c>
       <c r="G16">
-        <v>-7.842835818296582</v>
+        <v>-8.192270521057734</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.961042273085035</v>
       </c>
       <c r="E17">
-        <v>-20.68114436402545</v>
+        <v>-21.73330812886361</v>
       </c>
       <c r="F17">
-        <v>-1.391472658019853</v>
+        <v>-0.3802315539087172</v>
       </c>
       <c r="G17">
-        <v>-5.825405919392417</v>
+        <v>-7.560495941979839</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.136017143929354</v>
       </c>
       <c r="E18">
-        <v>-24.19653986601785</v>
+        <v>-22.10980092938732</v>
       </c>
       <c r="F18">
-        <v>-1.916193705649172</v>
+        <v>-0.761920058831451</v>
       </c>
       <c r="G18">
-        <v>-6.4381614143472</v>
+        <v>-8.326864060502345</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>4.271547319518343</v>
       </c>
       <c r="E19">
-        <v>-23.47084737781466</v>
+        <v>-22.44851267126503</v>
       </c>
       <c r="F19">
-        <v>-1.143545607831572</v>
+        <v>-0.2712034930870519</v>
       </c>
       <c r="G19">
-        <v>-7.056316409076534</v>
+        <v>-8.857537889356436</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>4.355265398250879</v>
       </c>
       <c r="E20">
-        <v>-24.44183824606534</v>
+        <v>-23.06188541865597</v>
       </c>
       <c r="F20">
-        <v>-1.264520383336412</v>
+        <v>0.3717040453692836</v>
       </c>
       <c r="G20">
-        <v>-5.252026053081726</v>
+        <v>-7.830278919066127</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.378310549491557</v>
       </c>
       <c r="E21">
-        <v>-27.00555229297577</v>
+        <v>-23.92414309750846</v>
       </c>
       <c r="F21">
-        <v>-1.199057820962778</v>
+        <v>0.3015048781864423</v>
       </c>
       <c r="G21">
-        <v>-8.449675368372688</v>
+        <v>-6.582617068953298</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>4.334393963870296</v>
       </c>
       <c r="E22">
-        <v>-24.04479975896883</v>
+        <v>-23.90338004418329</v>
       </c>
       <c r="F22">
-        <v>-0.7968506554727006</v>
+        <v>0.2566347010790015</v>
       </c>
       <c r="G22">
-        <v>-6.393833209576359</v>
+        <v>-7.24852006199554</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.220234561960666</v>
       </c>
       <c r="E23">
-        <v>-23.86038671195447</v>
+        <v>-25.22579860932521</v>
       </c>
       <c r="F23">
-        <v>-1.092797335633866</v>
+        <v>0.4117125341896941</v>
       </c>
       <c r="G23">
-        <v>-6.676984169550224</v>
+        <v>-7.372897257905959</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.036535620271794</v>
       </c>
       <c r="E24">
-        <v>-26.02031937397098</v>
+        <v>-25.42265137443864</v>
       </c>
       <c r="F24">
-        <v>-0.3721698823446724</v>
+        <v>0.3532306239194518</v>
       </c>
       <c r="G24">
-        <v>-6.028034480214589</v>
+        <v>-6.886038499264121</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.78829227209776</v>
       </c>
       <c r="E25">
-        <v>-26.27194856068119</v>
+        <v>-25.07777185096248</v>
       </c>
       <c r="F25">
-        <v>-0.7354172721462836</v>
+        <v>0.7560284153677255</v>
       </c>
       <c r="G25">
-        <v>-6.664702045599527</v>
+        <v>-7.55831098192392</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.482854260529277</v>
       </c>
       <c r="E26">
-        <v>-24.07384539125403</v>
+        <v>-25.85831774482058</v>
       </c>
       <c r="F26">
-        <v>-0.3111357721064049</v>
+        <v>0.5874647609394569</v>
       </c>
       <c r="G26">
-        <v>-6.611938570794623</v>
+        <v>-7.62822308262225</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.12973734957344</v>
       </c>
       <c r="E27">
-        <v>-27.60881295790758</v>
+        <v>-26.84540733816852</v>
       </c>
       <c r="F27">
-        <v>-0.1678166142784512</v>
+        <v>0.8688354882809621</v>
       </c>
       <c r="G27">
-        <v>-8.143949798366533</v>
+        <v>-7.467075657407146</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.740525683003057</v>
       </c>
       <c r="E28">
-        <v>-25.67467000991351</v>
+        <v>-25.36594129444059</v>
       </c>
       <c r="F28">
-        <v>0.7173254335741269</v>
+        <v>0.5658004682540414</v>
       </c>
       <c r="G28">
-        <v>-6.254575111466917</v>
+        <v>-7.596653720359759</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.327268517092869</v>
       </c>
       <c r="E29">
-        <v>-25.31243284556595</v>
+        <v>-24.34052722556574</v>
       </c>
       <c r="F29">
-        <v>-0.5035183028347704</v>
+        <v>1.191504472489037</v>
       </c>
       <c r="G29">
-        <v>-7.529674763009225</v>
+        <v>-7.230037286249789</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.907139445622949</v>
       </c>
       <c r="E30">
-        <v>-24.70906349725797</v>
+        <v>-25.40920180663586</v>
       </c>
       <c r="F30">
-        <v>0.2389540272336488</v>
+        <v>0.7492126083774912</v>
       </c>
       <c r="G30">
-        <v>-7.460093716864823</v>
+        <v>-8.454720639774537</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.495114465403248</v>
       </c>
       <c r="E31">
-        <v>-24.43348321152119</v>
+        <v>-25.78668181449324</v>
       </c>
       <c r="F31">
-        <v>-0.325397773680404</v>
+        <v>0.9624757962282239</v>
       </c>
       <c r="G31">
-        <v>-6.531813437107643</v>
+        <v>-8.641438718734971</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.105506066293339</v>
       </c>
       <c r="E32">
-        <v>-24.73531053260642</v>
+        <v>-24.79928881338679</v>
       </c>
       <c r="F32">
-        <v>-0.3342472226445111</v>
+        <v>0.8329820903529939</v>
       </c>
       <c r="G32">
-        <v>-7.79465082797249</v>
+        <v>-8.149991543975702</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.7513981526913988</v>
       </c>
       <c r="E33">
-        <v>-23.85275170477754</v>
+        <v>-24.50359757458195</v>
       </c>
       <c r="F33">
-        <v>-0.08269937853859359</v>
+        <v>0.644062963735733</v>
       </c>
       <c r="G33">
-        <v>-7.76766988182743</v>
+        <v>-7.216507086630788</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.4427427171119304</v>
       </c>
       <c r="E34">
-        <v>-26.15062168506768</v>
+        <v>-24.00946860476099</v>
       </c>
       <c r="F34">
-        <v>-0.4015073422822197</v>
+        <v>0.6894840051660356</v>
       </c>
       <c r="G34">
-        <v>-8.170695695778305</v>
+        <v>-7.024376265713645</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.1895333632365089</v>
       </c>
       <c r="E35">
-        <v>-25.18502422936015</v>
+        <v>-23.4485491718009</v>
       </c>
       <c r="F35">
-        <v>0.158927937551397</v>
+        <v>0.5488852058888755</v>
       </c>
       <c r="G35">
-        <v>-7.153778869752678</v>
+        <v>-6.794919043841221</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.003012430135686735</v>
       </c>
       <c r="E36">
-        <v>-21.85843439416955</v>
+        <v>-24.10708439047033</v>
       </c>
       <c r="F36">
-        <v>-0.1727346315488719</v>
+        <v>0.5254332963482187</v>
       </c>
       <c r="G36">
-        <v>-6.773314423651937</v>
+        <v>-7.508424371192643</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.1337147205746871</v>
       </c>
       <c r="E37">
-        <v>-24.56855400574797</v>
+        <v>-22.77792745600499</v>
       </c>
       <c r="F37">
-        <v>-0.8844397395425119</v>
+        <v>0.2929602684265654</v>
       </c>
       <c r="G37">
-        <v>-7.715743975043962</v>
+        <v>-7.265532955521855</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.2050379281984994</v>
       </c>
       <c r="E38">
-        <v>-21.41908184594537</v>
+        <v>-22.06116511854494</v>
       </c>
       <c r="F38">
-        <v>0.08667856104662691</v>
+        <v>0.1135764789829297</v>
       </c>
       <c r="G38">
-        <v>-7.391297270013228</v>
+        <v>-6.932833060461719</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.2226347042629337</v>
       </c>
       <c r="E39">
-        <v>-22.93437264754798</v>
+        <v>-21.6014706650783</v>
       </c>
       <c r="F39">
-        <v>0.1270672705049224</v>
+        <v>0.2099437724202073</v>
       </c>
       <c r="G39">
-        <v>-6.488951804010698</v>
+        <v>-6.817741944788956</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.1933578867965842</v>
       </c>
       <c r="E40">
-        <v>-20.66044018086238</v>
+        <v>-21.36440052230275</v>
       </c>
       <c r="F40">
-        <v>-0.722983477430263</v>
+        <v>0.5743773843426274</v>
       </c>
       <c r="G40">
-        <v>-7.08522409272545</v>
+        <v>-6.97838616708209</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.1254239749194593</v>
       </c>
       <c r="E41">
-        <v>-20.85967945177785</v>
+        <v>-21.16720812163875</v>
       </c>
       <c r="F41">
-        <v>-0.3492696654942801</v>
+        <v>0.8629623633951136</v>
       </c>
       <c r="G41">
-        <v>-4.833606202373241</v>
+        <v>-7.412799263290794</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.02845843423716714</v>
       </c>
       <c r="E42">
-        <v>-24.09046036238817</v>
+        <v>-20.52463577384636</v>
       </c>
       <c r="F42">
-        <v>-0.4628719711142043</v>
+        <v>0.04713644307399251</v>
       </c>
       <c r="G42">
-        <v>-6.90593818850068</v>
+        <v>-6.99305850491214</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.08714011417245528</v>
       </c>
       <c r="E43">
-        <v>-19.6871397908678</v>
+        <v>-21.16884290075552</v>
       </c>
       <c r="F43">
-        <v>-0.02699332743513244</v>
+        <v>0.4112635590573768</v>
       </c>
       <c r="G43">
-        <v>-6.610005212199689</v>
+        <v>-6.411663807850873</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.2108633543512708</v>
       </c>
       <c r="E44">
-        <v>-18.78144046085972</v>
+        <v>-19.91950937762339</v>
       </c>
       <c r="F44">
-        <v>-0.4211744411594856</v>
+        <v>0.2786551917476208</v>
       </c>
       <c r="G44">
-        <v>-6.580458593261693</v>
+        <v>-6.706054069930564</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.3323768240045347</v>
       </c>
       <c r="E45">
-        <v>-19.33264178859935</v>
+        <v>-19.79779758171923</v>
       </c>
       <c r="F45">
-        <v>-0.5609962318128198</v>
+        <v>0.4150897880909077</v>
       </c>
       <c r="G45">
-        <v>-7.146118267374804</v>
+        <v>-5.991356946185004</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.4420689120341565</v>
       </c>
       <c r="E46">
-        <v>-19.39746689401915</v>
+        <v>-17.05562090264052</v>
       </c>
       <c r="F46">
-        <v>-0.4153998919945702</v>
+        <v>0.1310848524085</v>
       </c>
       <c r="G46">
-        <v>-6.57752213936836</v>
+        <v>-6.279758431384153</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.5311731273308353</v>
       </c>
       <c r="E47">
-        <v>-17.37997738191391</v>
+        <v>-18.75177895610948</v>
       </c>
       <c r="F47">
-        <v>-0.2741259732841285</v>
+        <v>0.2543475786798721</v>
       </c>
       <c r="G47">
-        <v>-6.527470001360119</v>
+        <v>-7.143413551669219</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.5922428238892997</v>
       </c>
       <c r="E48">
-        <v>-18.7104656877375</v>
+        <v>-19.79948217405008</v>
       </c>
       <c r="F48">
-        <v>-0.5968057262684395</v>
+        <v>0.1648491077466079</v>
       </c>
       <c r="G48">
-        <v>-6.129572222449576</v>
+        <v>-7.493169377347681</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.6197267169663929</v>
       </c>
       <c r="E49">
-        <v>-18.1588069841231</v>
+        <v>-17.40242955604394</v>
       </c>
       <c r="F49">
-        <v>-0.6603216252454944</v>
+        <v>0.2798762052993472</v>
       </c>
       <c r="G49">
-        <v>-7.952305627643663</v>
+        <v>-6.245772370877995</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.6101471193896004</v>
       </c>
       <c r="E50">
-        <v>-16.99702244898126</v>
+        <v>-16.83066895630949</v>
       </c>
       <c r="F50">
-        <v>-1.006658722886357</v>
+        <v>0.2518020056510692</v>
       </c>
       <c r="G50">
-        <v>-6.118591142895813</v>
+        <v>-6.8143651883389</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.5621486697384409</v>
       </c>
       <c r="E51">
-        <v>-17.05828364535703</v>
+        <v>-16.24730640616739</v>
       </c>
       <c r="F51">
-        <v>-0.9591054637612482</v>
+        <v>-0.1171312980033579</v>
       </c>
       <c r="G51">
-        <v>-7.637012581029015</v>
+        <v>-6.498741087170323</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.476062808214002</v>
       </c>
       <c r="E52">
-        <v>-14.13682015184063</v>
+        <v>-15.78082829863726</v>
       </c>
       <c r="F52">
-        <v>-1.014246568296</v>
+        <v>0.2654294777945239</v>
       </c>
       <c r="G52">
-        <v>-8.420079091251603</v>
+        <v>-7.049258325986807</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.3532852371242487</v>
       </c>
       <c r="E53">
-        <v>-15.60537257321008</v>
+        <v>-16.12771393609882</v>
       </c>
       <c r="F53">
-        <v>-0.6980529320756091</v>
+        <v>0.172669724396438</v>
       </c>
       <c r="G53">
-        <v>-7.895688677831047</v>
+        <v>-7.61245826476424</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.19707575232424</v>
       </c>
       <c r="E54">
-        <v>-15.62390308884946</v>
+        <v>-16.53483733481041</v>
       </c>
       <c r="F54">
-        <v>-0.8784158517893539</v>
+        <v>0.1501696090015978</v>
       </c>
       <c r="G54">
-        <v>-9.407313565972125</v>
+        <v>-8.287713548954923</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.0122354435014737</v>
       </c>
       <c r="E55">
-        <v>-15.56076257576052</v>
+        <v>-14.69927473748932</v>
       </c>
       <c r="F55">
-        <v>0.196447182326395</v>
+        <v>-0.0649226140745162</v>
       </c>
       <c r="G55">
-        <v>-8.435886946201624</v>
+        <v>-7.63712182903181</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.1946470003105236</v>
       </c>
       <c r="E56">
-        <v>-14.35517864001649</v>
+        <v>-14.96624186566351</v>
       </c>
       <c r="F56">
-        <v>-0.4852304356831658</v>
+        <v>-0.02936660004415302</v>
       </c>
       <c r="G56">
-        <v>-8.202066425308438</v>
+        <v>-7.653085279622176</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.4152540735328494</v>
       </c>
       <c r="E57">
-        <v>-14.34198266675814</v>
+        <v>-13.83443582845245</v>
       </c>
       <c r="F57">
-        <v>-0.7656816752075636</v>
+        <v>0.4929314729319773</v>
       </c>
       <c r="G57">
-        <v>-9.481936572972836</v>
+        <v>-7.802519994719338</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.6423976732078497</v>
       </c>
       <c r="E58">
-        <v>-13.60223379523515</v>
+        <v>-14.32766363194588</v>
       </c>
       <c r="F58">
-        <v>0.0350919810372877</v>
+        <v>-0.06160583099370699</v>
       </c>
       <c r="G58">
-        <v>-8.249821044712425</v>
+        <v>-8.630997258104109</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.8682917625211189</v>
       </c>
       <c r="E59">
-        <v>-13.38863926171536</v>
+        <v>-14.93824231087409</v>
       </c>
       <c r="F59">
-        <v>0.007439420397034608</v>
+        <v>-0.1519914834153694</v>
       </c>
       <c r="G59">
-        <v>-7.784391447346289</v>
+        <v>-7.806330432635039</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.085651433361101</v>
       </c>
       <c r="E60">
-        <v>-14.24339325913715</v>
+        <v>-13.78646117481519</v>
       </c>
       <c r="F60">
-        <v>-0.1404332730441079</v>
+        <v>0.2772883855330016</v>
       </c>
       <c r="G60">
-        <v>-8.777025421841362</v>
+        <v>-7.74073197277438</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.288185224967649</v>
       </c>
       <c r="E61">
-        <v>-13.98381660054347</v>
+        <v>-12.89671113026213</v>
       </c>
       <c r="F61">
-        <v>-1.256693968114762</v>
+        <v>-0.4195939161549441</v>
       </c>
       <c r="G61">
-        <v>-9.535325740884662</v>
+        <v>-7.463794906777728</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.469385849276457</v>
       </c>
       <c r="E62">
-        <v>-13.17877166230388</v>
+        <v>-13.91880582768936</v>
       </c>
       <c r="F62">
-        <v>-0.578980088127597</v>
+        <v>-0.4129603499933257</v>
       </c>
       <c r="G62">
-        <v>-8.365825870954026</v>
+        <v>-8.160800475161423</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.626374803419566</v>
       </c>
       <c r="E63">
-        <v>-12.7800349974545</v>
+        <v>-13.01509449777065</v>
       </c>
       <c r="F63">
-        <v>-0.9826692029012829</v>
+        <v>-0.189549661458299</v>
       </c>
       <c r="G63">
-        <v>-7.718908856579505</v>
+        <v>-7.545065489221296</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.757808605625186</v>
       </c>
       <c r="E64">
-        <v>-12.04657164785416</v>
+        <v>-12.86247133829013</v>
       </c>
       <c r="F64">
-        <v>-0.9080656062377566</v>
+        <v>0.03017976233868664</v>
       </c>
       <c r="G64">
-        <v>-9.097304150038152</v>
+        <v>-7.580362525761005</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.863946122856499</v>
       </c>
       <c r="E65">
-        <v>-14.38109056828838</v>
+        <v>-13.781036062954</v>
       </c>
       <c r="F65">
-        <v>-0.7490000124499872</v>
+        <v>-0.830410304062317</v>
       </c>
       <c r="G65">
-        <v>-8.179316356362566</v>
+        <v>-6.984815246519354</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.946491894128962</v>
       </c>
       <c r="E66">
-        <v>-12.1853376768712</v>
+        <v>-13.6475457061559</v>
       </c>
       <c r="F66">
-        <v>-1.043914546827264</v>
+        <v>-0.3565021412881226</v>
       </c>
       <c r="G66">
-        <v>-7.785361437189295</v>
+        <v>-7.230325303711706</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.007721560142695</v>
       </c>
       <c r="E67">
-        <v>-12.50547361836945</v>
+        <v>-13.71683588694726</v>
       </c>
       <c r="F67">
-        <v>-0.8511087203560682</v>
+        <v>-0.3072242212303856</v>
       </c>
       <c r="G67">
-        <v>-7.135862197294142</v>
+        <v>-7.097317515580407</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.051489052321901</v>
       </c>
       <c r="E68">
-        <v>-11.70780556428835</v>
+        <v>-13.49857702519957</v>
       </c>
       <c r="F68">
-        <v>-1.506266155965003</v>
+        <v>-0.30794158740121</v>
       </c>
       <c r="G68">
-        <v>-7.742026396080235</v>
+        <v>-6.836870276914865</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.082631746205895</v>
       </c>
       <c r="E69">
-        <v>-13.52889063020692</v>
+        <v>-13.4023605379586</v>
       </c>
       <c r="F69">
-        <v>-0.4641774781410163</v>
+        <v>-0.3001665309585338</v>
       </c>
       <c r="G69">
-        <v>-7.48585969279697</v>
+        <v>-7.161919501233745</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.105642936610434</v>
       </c>
       <c r="E70">
-        <v>-12.21604978759122</v>
+        <v>-12.36219722924077</v>
       </c>
       <c r="F70">
-        <v>-0.7431045216442631</v>
+        <v>-0.5850437375160894</v>
       </c>
       <c r="G70">
-        <v>-8.029332090705886</v>
+        <v>-7.338556969027099</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.124314078133164</v>
       </c>
       <c r="E71">
-        <v>-13.64024127758152</v>
+        <v>-12.91763268017757</v>
       </c>
       <c r="F71">
-        <v>-1.20549423568253</v>
+        <v>-0.6389306938030028</v>
       </c>
       <c r="G71">
-        <v>-7.510735131979054</v>
+        <v>-6.471932289393306</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.141802718176369</v>
       </c>
       <c r="E72">
-        <v>-11.99349793248426</v>
+        <v>-14.66575950135855</v>
       </c>
       <c r="F72">
-        <v>-1.310979369122422</v>
+        <v>-0.5964892899205702</v>
       </c>
       <c r="G72">
-        <v>-7.800053638292581</v>
+        <v>-6.97156975381673</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.160055729877387</v>
       </c>
       <c r="E73">
-        <v>-13.3141549212372</v>
+        <v>-13.59554071065181</v>
       </c>
       <c r="F73">
-        <v>-0.4780460051986856</v>
+        <v>-0.5175574735774164</v>
       </c>
       <c r="G73">
-        <v>-7.254263858506176</v>
+        <v>-6.928032769429775</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.181583024306132</v>
       </c>
       <c r="E74">
-        <v>-13.11473903983543</v>
+        <v>-13.51625618772552</v>
       </c>
       <c r="F74">
-        <v>-2.095006749952279</v>
+        <v>-1.087460164457629</v>
       </c>
       <c r="G74">
-        <v>-7.443276145525325</v>
+        <v>-5.637357001125197</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.207185519835809</v>
       </c>
       <c r="E75">
-        <v>-14.71394699327417</v>
+        <v>-14.83427307613198</v>
       </c>
       <c r="F75">
-        <v>-0.7831801082243003</v>
+        <v>-0.9025006340257495</v>
       </c>
       <c r="G75">
-        <v>-7.213564011646376</v>
+        <v>-5.758956649328166</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.236319455511164</v>
       </c>
       <c r="E76">
-        <v>-13.03890068562897</v>
+        <v>-15.44530913093496</v>
       </c>
       <c r="F76">
-        <v>-2.100433384808018</v>
+        <v>-1.223617257720978</v>
       </c>
       <c r="G76">
-        <v>-6.570748763195011</v>
+        <v>-6.239091689979745</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.26718401532762</v>
       </c>
       <c r="E77">
-        <v>-14.08378719273681</v>
+        <v>-15.32856054254321</v>
       </c>
       <c r="F77">
-        <v>-1.746399925627746</v>
+        <v>-1.515249800448363</v>
       </c>
       <c r="G77">
-        <v>-6.942605790893647</v>
+        <v>-6.312605664224801</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.297079896856643</v>
       </c>
       <c r="E78">
-        <v>-14.58019851345763</v>
+        <v>-15.46733562850827</v>
       </c>
       <c r="F78">
-        <v>-1.647532619368819</v>
+        <v>-1.34494491773941</v>
       </c>
       <c r="G78">
-        <v>-6.500975705409331</v>
+        <v>-6.122265848444404</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.323589086380435</v>
       </c>
       <c r="E79">
-        <v>-14.14925081299169</v>
+        <v>-16.40656830854315</v>
       </c>
       <c r="F79">
-        <v>-1.566084222855961</v>
+        <v>-1.875763577820736</v>
       </c>
       <c r="G79">
-        <v>-5.803784746475437</v>
+        <v>-5.996796172506026</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.343189777399672</v>
       </c>
       <c r="E80">
-        <v>-15.433526041567</v>
+        <v>-15.47241657634487</v>
       </c>
       <c r="F80">
-        <v>-2.690955797078716</v>
+        <v>-1.457801692696815</v>
       </c>
       <c r="G80">
-        <v>-4.614262697123289</v>
+        <v>-5.224843163658771</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.352161776497264</v>
       </c>
       <c r="E81">
-        <v>-15.57875420299299</v>
+        <v>-16.73092478781654</v>
       </c>
       <c r="F81">
-        <v>-2.318878010763262</v>
+        <v>-1.875747838840083</v>
       </c>
       <c r="G81">
-        <v>-6.552332198360046</v>
+        <v>-4.800070376060424</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.34616633322249</v>
       </c>
       <c r="E82">
-        <v>-18.11772919639952</v>
+        <v>-18.06758087523858</v>
       </c>
       <c r="F82">
-        <v>-2.404621492259636</v>
+        <v>-2.019688272220137</v>
       </c>
       <c r="G82">
-        <v>-4.902876057236951</v>
+        <v>-5.345198046738974</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.322810721836688</v>
       </c>
       <c r="E83">
-        <v>-18.24420947543375</v>
+        <v>-18.8653802550659</v>
       </c>
       <c r="F83">
-        <v>-3.069390474843253</v>
+        <v>-1.758824608302336</v>
       </c>
       <c r="G83">
-        <v>-4.695682254116125</v>
+        <v>-4.885141464783076</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.279747880876748</v>
       </c>
       <c r="E84">
-        <v>-17.52727958443541</v>
+        <v>-19.76191848215646</v>
       </c>
       <c r="F84">
-        <v>-2.289890121869696</v>
+        <v>-2.010229973214972</v>
       </c>
       <c r="G84">
-        <v>-5.68167196371388</v>
+        <v>-5.412541164098829</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.215291761016999</v>
       </c>
       <c r="E85">
-        <v>-18.88376133106303</v>
+        <v>-19.93918559718671</v>
       </c>
       <c r="F85">
-        <v>-2.353261884918664</v>
+        <v>-2.005493368405764</v>
       </c>
       <c r="G85">
-        <v>-4.501889539338269</v>
+        <v>-5.2719522266826</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.128476539581863</v>
       </c>
       <c r="E86">
-        <v>-20.35311982080584</v>
+        <v>-19.74680243591886</v>
       </c>
       <c r="F86">
-        <v>-2.769106462961029</v>
+        <v>-1.835979576566484</v>
       </c>
       <c r="G86">
-        <v>-6.044438233361678</v>
+        <v>-4.58782468044667</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.018913662693857</v>
       </c>
       <c r="E87">
-        <v>-20.73500150539867</v>
+        <v>-20.26976872822066</v>
       </c>
       <c r="F87">
-        <v>-2.987193234198264</v>
+        <v>-2.251460501319021</v>
       </c>
       <c r="G87">
-        <v>-5.037866862146274</v>
+        <v>-4.775830561621881</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.888629807035832</v>
       </c>
       <c r="E88">
-        <v>-20.74002811154719</v>
+        <v>-22.37474382968008</v>
       </c>
       <c r="F88">
-        <v>-3.232585480133978</v>
+        <v>-2.228270355877649</v>
       </c>
       <c r="G88">
-        <v>-5.235688510845423</v>
+        <v>-5.004526358020273</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.740805254833015</v>
       </c>
       <c r="E89">
-        <v>-22.89120270483286</v>
+        <v>-23.41741591299816</v>
       </c>
       <c r="F89">
-        <v>-2.720970861551753</v>
+        <v>-2.272100103527174</v>
       </c>
       <c r="G89">
-        <v>-5.670899448529092</v>
+        <v>-4.611279895592406</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.57940360135419</v>
       </c>
       <c r="E90">
-        <v>-23.45633814709409</v>
+        <v>-24.63344703827789</v>
       </c>
       <c r="F90">
-        <v>-3.231879711106793</v>
+        <v>-2.561050392604295</v>
       </c>
       <c r="G90">
-        <v>-5.465562861455797</v>
+        <v>-5.519773044661362</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.409216144616236</v>
       </c>
       <c r="E91">
-        <v>-26.9626450017531</v>
+        <v>-24.93855750301868</v>
       </c>
       <c r="F91">
-        <v>-3.16544381703487</v>
+        <v>-2.435560186386795</v>
       </c>
       <c r="G91">
-        <v>-5.007823661377388</v>
+        <v>-5.630428029311502</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.235463460981244</v>
       </c>
       <c r="E92">
-        <v>-27.90102632867453</v>
+        <v>-29.13891186951527</v>
       </c>
       <c r="F92">
-        <v>-2.807772168221502</v>
+        <v>-2.212645689926045</v>
       </c>
       <c r="G92">
-        <v>-6.118303125433896</v>
+        <v>-5.647073452282958</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.064031717941868</v>
       </c>
       <c r="E93">
-        <v>-29.31564915308663</v>
+        <v>-28.82694076665285</v>
       </c>
       <c r="F93">
-        <v>-2.814070245584987</v>
+        <v>-2.187858452132075</v>
       </c>
       <c r="G93">
-        <v>-6.809833051495637</v>
+        <v>-5.732025361366195</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.9015017818024307</v>
       </c>
       <c r="E94">
-        <v>-31.32308545289484</v>
+        <v>-31.40096388464175</v>
       </c>
       <c r="F94">
-        <v>-3.188408646542681</v>
+        <v>-2.704738173926494</v>
       </c>
       <c r="G94">
-        <v>-5.962631342540748</v>
+        <v>-5.579799856379427</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.753338785641301</v>
       </c>
       <c r="E95">
-        <v>-33.53100182549662</v>
+        <v>-32.08493780604927</v>
       </c>
       <c r="F95">
-        <v>-2.552717844899534</v>
+        <v>-2.7798387910317</v>
       </c>
       <c r="G95">
-        <v>-7.014487666187843</v>
+        <v>-6.342936882455604</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.6237348947517901</v>
       </c>
       <c r="E96">
-        <v>-35.10964371422953</v>
+        <v>-33.68669076188033</v>
       </c>
       <c r="F96">
-        <v>-3.43152122538589</v>
+        <v>-2.455956248578524</v>
       </c>
       <c r="G96">
-        <v>-5.534862511229361</v>
+        <v>-6.156109555492374</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.5160099256964582</v>
       </c>
       <c r="E97">
-        <v>-35.09985994613596</v>
+        <v>-35.21868936833423</v>
       </c>
       <c r="F97">
-        <v>-3.91804211023511</v>
+        <v>-2.477605630650689</v>
       </c>
       <c r="G97">
-        <v>-7.907278897764035</v>
+        <v>-6.954546928653798</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.4316278545230118</v>
       </c>
       <c r="E98">
-        <v>-39.36001281190384</v>
+        <v>-37.60645408615064</v>
       </c>
       <c r="F98">
-        <v>-3.682991202955945</v>
+        <v>-3.048578572215318</v>
       </c>
       <c r="G98">
-        <v>-7.245010883723913</v>
+        <v>-7.200884622230967</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.372888245990965</v>
       </c>
       <c r="E99">
-        <v>-40.34648200431272</v>
+        <v>-40.81247556512402</v>
       </c>
       <c r="F99">
-        <v>-3.948434081876421</v>
+        <v>-2.579180869949367</v>
       </c>
       <c r="G99">
-        <v>-8.345436220977655</v>
+        <v>-7.556910621160808</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.3398732165281105</v>
       </c>
       <c r="E100">
-        <v>-42.22235028453908</v>
+        <v>-43.10338980933839</v>
       </c>
       <c r="F100">
-        <v>-3.579041034313441</v>
+        <v>-2.663451514203564</v>
       </c>
       <c r="G100">
-        <v>-8.542205116195317</v>
+        <v>-8.327642038704074</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.3331302056204051</v>
       </c>
       <c r="E101">
-        <v>-46.80810722416946</v>
+        <v>-43.83368322713336</v>
       </c>
       <c r="F101">
-        <v>-3.449970624181041</v>
+        <v>-2.739015188686935</v>
       </c>
       <c r="G101">
-        <v>-7.580266519940367</v>
+        <v>-8.442610664191882</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.3515384912875685</v>
       </c>
       <c r="E102">
-        <v>-46.15861989656736</v>
+        <v>-46.63472327560078</v>
       </c>
       <c r="F102">
-        <v>-4.52982540026606</v>
+        <v>-2.739185832371911</v>
       </c>
       <c r="G102">
-        <v>-8.739692399795</v>
+        <v>-8.70035318715184</v>
       </c>
     </row>
   </sheetData>
